--- a/data/trans_dic/P36B06_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,73; 69,47</t>
+          <t>61,24; 69,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,71; 77,11</t>
+          <t>68,91; 77,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,04; 73,76</t>
+          <t>64,71; 74,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,29; 70,76</t>
+          <t>62,84; 71,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,21; 81,21</t>
+          <t>72,88; 80,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,69; 70,88</t>
+          <t>61,29; 70,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,14; 69,07</t>
+          <t>62,98; 69,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72,08; 77,86</t>
+          <t>71,97; 77,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,7; 71,13</t>
+          <t>64,47; 70,95</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,57; 75,37</t>
+          <t>68,99; 75,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,08; 79,48</t>
+          <t>73,09; 79,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,79; 78,27</t>
+          <t>70,62; 78,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,2; 81,68</t>
+          <t>74,72; 81,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,86; 87,71</t>
+          <t>81,81; 87,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,5; 78,64</t>
+          <t>71,83; 78,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,78; 77,6</t>
+          <t>72,34; 77,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,08; 82,87</t>
+          <t>78,12; 82,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72,41; 77,39</t>
+          <t>72,53; 77,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,74; 80,77</t>
+          <t>73,92; 80,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,51; 85,15</t>
+          <t>79,46; 85,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,64; 80,41</t>
+          <t>73,76; 80,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,36; 85,26</t>
+          <t>79,36; 85,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,32; 89,33</t>
+          <t>84,59; 89,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,55; 87,06</t>
+          <t>81,58; 87,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,72; 82,05</t>
+          <t>77,54; 82,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,85; 86,79</t>
+          <t>82,71; 86,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78,63; 82,9</t>
+          <t>78,81; 82,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,18; 82,69</t>
+          <t>75,08; 82,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,58; 89,47</t>
+          <t>83,81; 89,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,5; 83,33</t>
+          <t>76,72; 83,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,21; 88,61</t>
+          <t>81,98; 88,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,68; 93,01</t>
+          <t>87,91; 92,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,48; 89,09</t>
+          <t>83,11; 88,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,54; 84,3</t>
+          <t>79,85; 84,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,53; 90,51</t>
+          <t>86,71; 90,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,05; 85,33</t>
+          <t>81,04; 85,4</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,1; 85,0</t>
+          <t>77,3; 85,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,6; 92,47</t>
+          <t>86,47; 92,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,52; 89,3</t>
+          <t>82,66; 89,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,46; 90,1</t>
+          <t>82,94; 90,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,93; 90,85</t>
+          <t>84,03; 90,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,52; 91,09</t>
+          <t>84,6; 91,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,32; 86,57</t>
+          <t>81,45; 86,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,86; 90,53</t>
+          <t>86,29; 90,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,78; 89,33</t>
+          <t>84,92; 89,48</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80,78; 88,98</t>
+          <t>80,42; 88,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,5; 93,97</t>
+          <t>87,21; 94,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,39; 94,25</t>
+          <t>87,7; 94,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,75; 92,17</t>
+          <t>85,27; 91,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,22; 96,18</t>
+          <t>91,4; 96,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,3; 93,37</t>
+          <t>87,39; 93,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,43; 89,63</t>
+          <t>84,19; 89,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,55; 94,73</t>
+          <t>90,56; 94,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,58; 93,01</t>
+          <t>88,28; 93,01</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>79,87; 89,33</t>
+          <t>78,86; 89,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,83</t>
+          <t>91,5; 97,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,25; 93,07</t>
+          <t>86,51; 93,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,16; 90,28</t>
+          <t>82,78; 90,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,26; 96,92</t>
+          <t>91,93; 96,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,46; 95,39</t>
+          <t>89,44; 95,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,43; 88,57</t>
+          <t>82,65; 88,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,85; 96,74</t>
+          <t>93,01; 96,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,04; 93,85</t>
+          <t>89,33; 93,88</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,82; 77,73</t>
+          <t>74,89; 77,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,2; 84,75</t>
+          <t>81,88; 84,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,54; 81,24</t>
+          <t>78,62; 81,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,24; 82,89</t>
+          <t>80,35; 82,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,71; 88,83</t>
+          <t>86,48; 88,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,12; 84,59</t>
+          <t>82,13; 84,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,85; 80,03</t>
+          <t>77,96; 80,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,79; 86,48</t>
+          <t>84,72; 86,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80,71; 82,65</t>
+          <t>80,81; 82,67</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>299430; 342480</t>
+          <t>301942; 343043</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>312064; 350174</t>
+          <t>312955; 351381</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272191; 308681</t>
+          <t>270795; 309932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290556; 330067</t>
+          <t>293125; 331978</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>314980; 349399</t>
+          <t>313549; 348436</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>243530; 279802</t>
+          <t>241945; 277998</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>605783; 662705</t>
+          <t>604272; 662621</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>637468; 688559</t>
+          <t>636471; 689055</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>526174; 578466</t>
+          <t>524309; 577007</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>503690; 553647</t>
+          <t>506754; 554642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>501436; 545321</t>
+          <t>501516; 546181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>417305; 461416</t>
+          <t>416320; 460133</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>470401; 510895</t>
+          <t>467360; 507817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>498771; 534399</t>
+          <t>498469; 534702</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>402920; 443167</t>
+          <t>404787; 442685</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>989841; 1055453</t>
+          <t>983873; 1050528</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1011458; 1073559</t>
+          <t>1011924; 1069443</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>834893; 892404</t>
+          <t>836361; 892300</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>470327; 515161</t>
+          <t>471440; 513880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>542154; 580582</t>
+          <t>541813; 580555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>491405; 536539</t>
+          <t>492176; 537784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>547373; 588080</t>
+          <t>547388; 587870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>598385; 633983</t>
+          <t>600332; 634855</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>538035; 574358</t>
+          <t>538258; 574284</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1031712; 1089181</t>
+          <t>1029371; 1089515</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1152868; 1207769</t>
+          <t>1150923; 1205305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1043389; 1100097</t>
+          <t>1045833; 1101350</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>390277; 429262</t>
+          <t>389779; 426312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511995; 548059</t>
+          <t>513360; 547537</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>494231; 538355</t>
+          <t>495647; 538704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423119; 456057</t>
+          <t>421925; 454403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>539351; 572163</t>
+          <t>540760; 571607</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>540912; 577257</t>
+          <t>538541; 575621</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>822330; 871532</t>
+          <t>825522; 874018</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1062381; 1111188</t>
+          <t>1064517; 1112607</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1048756; 1104184</t>
+          <t>1048697; 1105100</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>298156; 328715</t>
+          <t>298941; 328904</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>371902; 397110</t>
+          <t>371344; 397513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>393497; 425860</t>
+          <t>394167; 425288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>337168; 364002</t>
+          <t>335054; 363754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>375821; 406805</t>
+          <t>376266; 406298</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>419944; 452558</t>
+          <t>420329; 452941</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>642992; 684503</t>
+          <t>644059; 685590</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>753199; 794139</t>
+          <t>756984; 795800</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>825502; 869809</t>
+          <t>826914; 871239</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>236341; 260327</t>
+          <t>235281; 258863</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>270213; 290183</t>
+          <t>269312; 290350</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>291253; 314093</t>
+          <t>292276; 313665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>294074; 316072</t>
+          <t>292413; 315044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>322903; 340478</t>
+          <t>323536; 341152</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>327974; 350775</t>
+          <t>328291; 351136</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>536546; 569622</t>
+          <t>535068; 569473</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>600145; 627880</t>
+          <t>600255; 627121</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>627972; 659359</t>
+          <t>625860; 659413</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>167632; 187479</t>
+          <t>165516; 187327</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>227248; 243391</t>
+          <t>227632; 243268</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>220895; 238358</t>
+          <t>221541; 239025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274339; 301455</t>
+          <t>276406; 301469</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>355084; 373027</t>
+          <t>353797; 372770</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>357990; 381735</t>
+          <t>357891; 381635</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>448250; 481624</t>
+          <t>449438; 483048</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>588358; 612969</t>
+          <t>589359; 612722</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>584316; 615894</t>
+          <t>586217; 616137</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2449382; 2544630</t>
+          <t>2451498; 2550722</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2812667; 2899943</t>
+          <t>2801621; 2893006</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2660576; 2752130</t>
+          <t>2663191; 2759808</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2709677; 2799375</t>
+          <t>2713392; 2798214</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3078892; 3154466</t>
+          <t>3070752; 3152914</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2905980; 2993329</t>
+          <t>2906414; 2999309</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5177785; 5322608</t>
+          <t>5185270; 5322071</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5912374; 6029929</t>
+          <t>5907117; 6026951</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5590496; 5724540</t>
+          <t>5597182; 5726172</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B06_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,24; 69,58</t>
+          <t>60,66; 69,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,91; 77,37</t>
+          <t>68,71; 76,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,71; 74,06</t>
+          <t>64,94; 73,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,84; 71,17</t>
+          <t>62,34; 70,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,88; 80,99</t>
+          <t>72,78; 80,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,29; 70,42</t>
+          <t>61,62; 70,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,98; 69,06</t>
+          <t>63,14; 69,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,97; 77,91</t>
+          <t>71,92; 77,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,47; 70,95</t>
+          <t>64,72; 71,17</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,99; 75,51</t>
+          <t>68,48; 75,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,09; 79,6</t>
+          <t>72,83; 79,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,62; 78,05</t>
+          <t>71,07; 78,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,72; 81,19</t>
+          <t>75,0; 81,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,81; 87,76</t>
+          <t>81,67; 87,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,83; 78,55</t>
+          <t>71,52; 78,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,34; 77,24</t>
+          <t>72,68; 77,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,12; 82,56</t>
+          <t>77,81; 82,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72,53; 77,39</t>
+          <t>72,02; 77,3</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,92; 80,57</t>
+          <t>73,86; 80,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,46; 85,14</t>
+          <t>79,63; 85,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,76; 80,59</t>
+          <t>73,77; 80,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,36; 85,23</t>
+          <t>79,39; 84,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,59; 89,46</t>
+          <t>84,18; 89,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,58; 87,04</t>
+          <t>81,24; 86,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,54; 82,07</t>
+          <t>77,69; 82,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,71; 86,62</t>
+          <t>82,75; 86,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78,81; 82,99</t>
+          <t>78,65; 83,09</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,08; 82,12</t>
+          <t>75,08; 82,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,81; 89,38</t>
+          <t>83,92; 89,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,72; 83,38</t>
+          <t>76,58; 83,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81,98; 88,29</t>
+          <t>81,93; 88,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,91; 92,92</t>
+          <t>87,82; 92,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,11; 88,84</t>
+          <t>83,53; 89,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,85; 84,54</t>
+          <t>79,62; 84,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,71; 90,63</t>
+          <t>86,58; 90,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,04; 85,4</t>
+          <t>80,82; 85,35</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,3; 85,05</t>
+          <t>77,31; 84,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,47; 92,57</t>
+          <t>86,47; 92,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,66; 89,18</t>
+          <t>82,54; 89,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,94; 90,04</t>
+          <t>83,22; 89,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,03; 90,73</t>
+          <t>84,57; 91,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,6; 91,16</t>
+          <t>84,71; 90,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,45; 86,71</t>
+          <t>81,47; 86,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,29; 90,72</t>
+          <t>86,04; 90,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,92; 89,48</t>
+          <t>84,77; 89,25</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80,42; 88,48</t>
+          <t>80,29; 88,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,21; 94,02</t>
+          <t>87,32; 94,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,7; 94,12</t>
+          <t>87,68; 94,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,27; 91,87</t>
+          <t>85,66; 92,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,4; 96,37</t>
+          <t>91,1; 96,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,39; 93,47</t>
+          <t>87,3; 93,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,19; 89,61</t>
+          <t>84,47; 89,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,56; 94,62</t>
+          <t>90,47; 94,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,28; 93,01</t>
+          <t>88,72; 92,98</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,86; 89,25</t>
+          <t>79,07; 88,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,5; 97,78</t>
+          <t>91,75; 97,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,51; 93,33</t>
+          <t>86,33; 93,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,78; 90,29</t>
+          <t>82,7; 90,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,93; 96,86</t>
+          <t>92,17; 96,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,44; 95,37</t>
+          <t>89,28; 95,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,65; 88,83</t>
+          <t>82,66; 88,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,01; 96,7</t>
+          <t>92,74; 96,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,33; 93,88</t>
+          <t>89,37; 93,76</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,89; 77,92</t>
+          <t>74,74; 77,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,88; 84,55</t>
+          <t>82,04; 84,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,47</t>
+          <t>78,63; 81,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,35; 82,86</t>
+          <t>80,33; 82,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,48; 88,79</t>
+          <t>86,68; 88,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,13; 84,76</t>
+          <t>82,03; 84,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,96; 80,02</t>
+          <t>78,01; 79,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,72; 86,44</t>
+          <t>84,73; 86,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80,81; 82,67</t>
+          <t>80,73; 82,71</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>301942; 343043</t>
+          <t>299080; 342993</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>312955; 351381</t>
+          <t>312043; 348610</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>270795; 309932</t>
+          <t>271767; 309342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293125; 331978</t>
+          <t>290751; 330468</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>313549; 348436</t>
+          <t>313117; 347598</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>241945; 277998</t>
+          <t>243246; 279018</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>604272; 662621</t>
+          <t>605775; 662260</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>636471; 689055</t>
+          <t>636013; 688255</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>524309; 577007</t>
+          <t>526328; 578787</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>506754; 554642</t>
+          <t>503045; 553530</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>501516; 546181</t>
+          <t>499702; 545453</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>416320; 460133</t>
+          <t>418960; 460480</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>467360; 507817</t>
+          <t>469151; 509798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>498469; 534702</t>
+          <t>497594; 533508</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>404787; 442685</t>
+          <t>403052; 444233</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>983873; 1050528</t>
+          <t>988484; 1051972</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1011924; 1069443</t>
+          <t>1007895; 1068677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>836361; 892300</t>
+          <t>830468; 891314</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>471440; 513880</t>
+          <t>471057; 513234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>541813; 580555</t>
+          <t>542991; 584250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492176; 537784</t>
+          <t>492232; 536613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>547388; 587870</t>
+          <t>547622; 585944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>600332; 634855</t>
+          <t>597368; 636592</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>538258; 574284</t>
+          <t>535954; 573608</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1029371; 1089515</t>
+          <t>1031415; 1090045</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1150923; 1205305</t>
+          <t>1151515; 1205797</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1045833; 1101350</t>
+          <t>1043726; 1102663</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>389779; 426312</t>
+          <t>389799; 428463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>513360; 547537</t>
+          <t>514075; 548215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>495647; 538704</t>
+          <t>494755; 537205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>421925; 454403</t>
+          <t>421668; 454464</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>540760; 571607</t>
+          <t>540189; 571984</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>538541; 575621</t>
+          <t>541267; 577001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>825522; 874018</t>
+          <t>823129; 874124</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1064517; 1112607</t>
+          <t>1062891; 1113227</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1048697; 1105100</t>
+          <t>1045842; 1104379</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>298941; 328904</t>
+          <t>298962; 328282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>371344; 397513</t>
+          <t>371333; 397354</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>394167; 425288</t>
+          <t>393586; 424593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>335054; 363754</t>
+          <t>336206; 363256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>376266; 406298</t>
+          <t>378717; 407794</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>420329; 452941</t>
+          <t>420870; 451515</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>644059; 685590</t>
+          <t>644185; 684962</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>756984; 795800</t>
+          <t>754748; 796017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>826914; 871239</t>
+          <t>825399; 869037</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>235281; 258863</t>
+          <t>234921; 259223</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269312; 290350</t>
+          <t>269638; 290960</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>292276; 313665</t>
+          <t>292217; 313920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>292413; 315044</t>
+          <t>293774; 316712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>323536; 341152</t>
+          <t>322473; 340708</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>328291; 351136</t>
+          <t>327960; 350655</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>535068; 569473</t>
+          <t>536793; 568936</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>600255; 627121</t>
+          <t>599623; 626540</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>625860; 659413</t>
+          <t>628996; 659153</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>165516; 187327</t>
+          <t>165963; 186614</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>227632; 243268</t>
+          <t>228269; 243434</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221541; 239025</t>
+          <t>221100; 239113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>276406; 301469</t>
+          <t>276143; 302448</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>353797; 372770</t>
+          <t>354718; 372440</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>357891; 381635</t>
+          <t>357281; 380835</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>449438; 483048</t>
+          <t>449475; 481813</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>589359; 612722</t>
+          <t>587630; 612624</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>586217; 616137</t>
+          <t>586476; 615326</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2451498; 2550722</t>
+          <t>2446669; 2543041</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2801621; 2893006</t>
+          <t>2807106; 2901259</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2663191; 2759808</t>
+          <t>2663723; 2756120</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2713392; 2798214</t>
+          <t>2712791; 2798060</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3070752; 3152914</t>
+          <t>3078052; 3157898</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2906414; 2999309</t>
+          <t>2902820; 2994356</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5185270; 5322071</t>
+          <t>5188156; 5314879</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5907117; 6026951</t>
+          <t>5907769; 6028474</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5597182; 5726172</t>
+          <t>5591746; 5728970</t>
         </is>
       </c>
     </row>
